--- a/Resultados estadisticos horizontes.xlsx
+++ b/Resultados estadisticos horizontes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\James Kagunda\Desktop\TFG\CODING\PROYECTO-FINAL-TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B0E25A-2155-41F7-A41C-09332DA26A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA27FD2C-B0CD-46BA-9DF9-5385C0967943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8DF222DA-5841-4DCA-8F0C-428A0B296B9D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="19">
   <si>
     <t>GRU</t>
   </si>
@@ -87,13 +87,22 @@
   </si>
   <si>
     <t>RESULTADOS PARA HORIZONTE TEMPORAL T = 4h</t>
+  </si>
+  <si>
+    <t>Nmae(% rango fisico)</t>
+  </si>
+  <si>
+    <t>nRMSE(% rango fisico)</t>
+  </si>
+  <si>
+    <t>MAPE (clasico filtrado)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,6 +127,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFBBBEBF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF002060"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -129,6 +145,19 @@
       <color rgb="FF002060"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -169,7 +198,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -218,11 +247,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -232,28 +272,41 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,10 +641,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C2D3613-5EAE-4D23-8D47-435E6ECA8C80}">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -612,7 +665,7 @@
       <c r="I1" s="16"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -634,7 +687,7 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="18" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -664,7 +717,7 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="18" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2"/>
@@ -678,7 +731,7 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="18" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2"/>
@@ -692,7 +745,7 @@
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="18" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2"/>
@@ -703,9 +756,10 @@
       <c r="G6" s="4"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
+      <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="18" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2"/>
@@ -716,200 +770,201 @@
       <c r="G7" s="4"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
+      <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F8" s="1"/>
+      <c r="A8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F9" s="1"/>
+      <c r="A9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F11" s="1"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="12"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="K14" s="1"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="12"/>
+      <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="K19" s="17"/>
+    </row>
+    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="12"/>
-      <c r="H20" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="12"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>3</v>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="K20" s="17"/>
+    </row>
+    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>17</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -919,10 +974,11 @@
       <c r="G22" s="4"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>4</v>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>18</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -932,217 +988,396 @@
       <c r="G23" s="4"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F24" s="1"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" spans="1:11" s="19" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F25" s="20"/>
+      <c r="K25" s="21"/>
+    </row>
+    <row r="26" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="D27" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="12"/>
+      <c r="F27" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="12"/>
+      <c r="H27" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="12"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B39" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="13" t="s">
+      <c r="C39" s="12"/>
+      <c r="D39" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="14" t="s">
+      <c r="E39" s="12"/>
+      <c r="F39" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="12"/>
-      <c r="H29" s="15" t="s">
+      <c r="G39" s="12"/>
+      <c r="H39" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I29" s="12"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="I39" s="12"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="B40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B41" s="2">
         <v>6.8500000000000005E-2</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C41" s="2">
         <v>5.9400000000000001E-2</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D41" s="3">
         <v>7.3800000000000004E-2</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E41" s="3">
         <v>6.5199999999999994E-2</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F41" s="4">
         <v>6.13E-2</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G41" s="4">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H41" s="5">
         <v>6.3299999999999995E-2</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I41" s="5">
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B42" s="2">
         <v>0.1215</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C42" s="2">
         <v>0.113</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D42" s="3">
         <v>0.1305</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E42" s="3">
         <v>0.1244</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F42" s="4">
         <v>0.10639999999999999</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G42" s="4">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H42" s="5">
         <v>0.1022</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I42" s="5">
         <v>0.10639999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B43" s="2">
         <v>-2.0000000000000001E-4</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C43" s="2">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D43" s="3">
         <v>1E-4</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E43" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F43" s="4">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G43" s="4">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H43" s="5">
         <v>-2.9999999999999997E-4</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I43" s="5">
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B44" s="2">
         <v>0.75419999999999998</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C44" s="2">
         <v>0.88560000000000005</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D44" s="3">
         <v>0.76749999999999996</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E44" s="3">
         <v>0.79469999999999996</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F44" s="4">
         <v>0.58299999999999996</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G44" s="4">
         <v>0.5867</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H44" s="5">
         <v>0.58989999999999998</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I44" s="5">
         <v>0.58730000000000004</v>
       </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -1150,22 +1385,22 @@
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
